--- a/leads.xlsx
+++ b/leads.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\safim\OneDrive\Desktop\master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\safim\OneDrive\Desktop\coldemail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5F87D0-A0CE-4C79-83C7-A551AA4B82D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1B346D-8D91-4CDE-A6D7-48F73526D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
   <si>
     <t>Niche</t>
   </si>
@@ -221,6 +221,33 @@
   </si>
   <si>
     <t>Services: General contracting, roof installations, repairs, home extensions. Owner: John Dewis (Companies House: The Building &amp; Landscaping Company Ltd). Address: 14 Potters Rd, Bedworth, CV12 0DH.</t>
+  </si>
+  <si>
+    <t>Roofing contractor</t>
+  </si>
+  <si>
+    <t>Loughrea, Co. Galway</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/FoxRoofingAndConstructionLimited</t>
+  </si>
+  <si>
+    <t>Fox Roofing and Construction Limited</t>
+  </si>
+  <si>
+    <t>John Fox</t>
+  </si>
+  <si>
+    <t>+353 83 067 4929</t>
+  </si>
+  <si>
+    <t>johnfoxroofing@gmail.com</t>
+  </si>
+  <si>
+    <t>https://coldemail-ruddy.vercel.app/coldemail/FoxRoofingandConstructionLimited/index.html</t>
+  </si>
+  <si>
+    <t>Formally established in May 2026. Local, family-run business. Specializes in roofing repairs, VELUX installations, chimney repairs, and leak detection.</t>
   </si>
 </sst>
 </file>
@@ -576,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -859,6 +886,59 @@
         <v>66</v>
       </c>
     </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N6" s="2">
+        <v>46257</v>
+      </c>
+      <c r="O6" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" t="s">
+        <v>35</v>
+      </c>
+      <c r="V6" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\safim\OneDrive\Desktop\coldemail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1B346D-8D91-4CDE-A6D7-48F73526D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF350F0-1528-4CD9-A83F-80C9DAFB4CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="94">
   <si>
     <t>Niche</t>
   </si>
@@ -248,6 +248,60 @@
   </si>
   <si>
     <t>Formally established in May 2026. Local, family-run business. Specializes in roofing repairs, VELUX installations, chimney repairs, and leak detection.</t>
+  </si>
+  <si>
+    <t>Limerick, Ireland</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/people/Mc-Roofing-And-Guttering/</t>
+  </si>
+  <si>
+    <t>https://mc-roofingandguttering.com</t>
+  </si>
+  <si>
+    <t>MC Roofing and Guttering</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>(087) 187 1948</t>
+  </si>
+  <si>
+    <t>mcroofingguttering@gmail.com</t>
+  </si>
+  <si>
+    <t>https://coldemail-ruddy.vercel.app/coldemail/MCRoofingandGuttering/index.html</t>
+  </si>
+  <si>
+    <t>Google Maps / Web Search</t>
+  </si>
+  <si>
+    <t>Based in Crossgalla Industrial Estate, Limerick. Owner is William.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/search/top?q=Alupro%20Roofers</t>
+  </si>
+  <si>
+    <t>https://aluproroofers.com</t>
+  </si>
+  <si>
+    <t>AluPro Roofers Limerick</t>
+  </si>
+  <si>
+    <t>085 7700458</t>
+  </si>
+  <si>
+    <t>info@aluproroofers.com</t>
+  </si>
+  <si>
+    <t>aluproroofing@gmail.com</t>
+  </si>
+  <si>
+    <t>https://coldemail-ruddy.vercel.app/coldemail/AluProRoofersLimerick/index.html</t>
+  </si>
+  <si>
+    <t>Based in Raheen Business Park, Limerick. 30+ years experience.</t>
   </si>
 </sst>
 </file>
@@ -603,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -939,6 +993,112 @@
         <v>75</v>
       </c>
     </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7" s="2">
+        <v>46257</v>
+      </c>
+      <c r="O7" t="s">
+        <v>84</v>
+      </c>
+      <c r="T7" t="s">
+        <v>35</v>
+      </c>
+      <c r="V7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" s="2">
+        <v>46257</v>
+      </c>
+      <c r="O8" t="s">
+        <v>84</v>
+      </c>
+      <c r="T8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V8" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\safim\OneDrive\Desktop\coldemail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF350F0-1528-4CD9-A83F-80C9DAFB4CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6C9C07-3004-4AA7-887E-4E0839D7F6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="101">
   <si>
     <t>Niche</t>
   </si>
@@ -302,6 +302,27 @@
   </si>
   <si>
     <t>Based in Raheen Business Park, Limerick. 30+ years experience.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/search/top?q=WL%20Roofing%20Limited</t>
+  </si>
+  <si>
+    <t>https://wlroofingltd.com</t>
+  </si>
+  <si>
+    <t>WL Roofing Limited</t>
+  </si>
+  <si>
+    <t>085 103 4237</t>
+  </si>
+  <si>
+    <t>wlroofingltd@gmail.com</t>
+  </si>
+  <si>
+    <t>https://coldemail-ruddy.vercel.app/coldemail/WLRoofingLimited/index.html</t>
+  </si>
+  <si>
+    <t>105 BrÃº Na GruadÃ¡n, Newcastle, Limerick. Family-owned Irish company.</t>
   </si>
 </sst>
 </file>
@@ -657,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1099,6 +1120,59 @@
         <v>93</v>
       </c>
     </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" s="2">
+        <v>46257</v>
+      </c>
+      <c r="O9" t="s">
+        <v>84</v>
+      </c>
+      <c r="T9" t="s">
+        <v>35</v>
+      </c>
+      <c r="V9" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\safim\OneDrive\Desktop\coldemail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6C9C07-3004-4AA7-887E-4E0839D7F6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8B51CC-E116-48BC-B9B2-AC4765725EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="109">
   <si>
     <t>Niche</t>
   </si>
@@ -323,6 +323,30 @@
   </si>
   <si>
     <t>105 BrÃº Na GruadÃ¡n, Newcastle, Limerick. Family-owned Irish company.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/search/top?q=Doherty%20Roofing%20Limerick</t>
+  </si>
+  <si>
+    <t>https://dohertyroofing.ie</t>
+  </si>
+  <si>
+    <t>Doherty Roofing</t>
+  </si>
+  <si>
+    <t>Jim Doherty</t>
+  </si>
+  <si>
+    <t>(083) 018 7199</t>
+  </si>
+  <si>
+    <t>info@dohertyroofing.ie</t>
+  </si>
+  <si>
+    <t>https://coldemail-ruddy.vercel.app/coldemail/DohertyRoofing/index.html</t>
+  </si>
+  <si>
+    <t>Family-run roofing company led by Jim Doherty. Based in Ballykeeffe Estate, Limerick.</t>
   </si>
 </sst>
 </file>
@@ -678,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1173,6 +1197,59 @@
         <v>100</v>
       </c>
     </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" t="s">
+        <v>106</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" t="s">
+        <v>107</v>
+      </c>
+      <c r="N10" s="2">
+        <v>46257</v>
+      </c>
+      <c r="O10" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" t="s">
+        <v>35</v>
+      </c>
+      <c r="V10" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\safim\OneDrive\Desktop\coldemail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8B51CC-E116-48BC-B9B2-AC4765725EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE600552-4034-4587-8F2F-EA2C48BA95EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="116">
   <si>
     <t>Niche</t>
   </si>
@@ -347,6 +347,27 @@
   </si>
   <si>
     <t>Family-run roofing company led by Jim Doherty. Based in Ballykeeffe Estate, Limerick.</t>
+  </si>
+  <si>
+    <t>Cobh, Cork, Ireland</t>
+  </si>
+  <si>
+    <t>https://greatislandroofingltd.com</t>
+  </si>
+  <si>
+    <t>Great Island Roofing Ltd.</t>
+  </si>
+  <si>
+    <t>(089) 982 4970</t>
+  </si>
+  <si>
+    <t>greatislandroofingltd@gmail.com</t>
+  </si>
+  <si>
+    <t>https://coldemail-ruddy.vercel.app/coldemail/GreatIslandRoofingLtd/index.html</t>
+  </si>
+  <si>
+    <t>Services: Roofing repairs, installations, flat roofing, guttering systems, emergency services. Serving Cobh, Cork area.</t>
   </si>
 </sst>
 </file>
@@ -702,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1250,6 +1271,59 @@
         <v>108</v>
       </c>
     </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>114</v>
+      </c>
+      <c r="N11" s="2">
+        <v>46257</v>
+      </c>
+      <c r="O11" t="s">
+        <v>34</v>
+      </c>
+      <c r="T11" t="s">
+        <v>35</v>
+      </c>
+      <c r="V11" t="s">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\safim\OneDrive\Desktop\coldemail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE600552-4034-4587-8F2F-EA2C48BA95EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888DE146-C51A-4B09-972F-3E3DB53C4584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="127">
   <si>
     <t>Niche</t>
   </si>
@@ -368,6 +368,39 @@
   </si>
   <si>
     <t>Services: Roofing repairs, installations, flat roofing, guttering systems, emergency services. Serving Cobh, Cork area.</t>
+  </si>
+  <si>
+    <t>Fairfax, VA</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/usastormroofing/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/usastormroofing</t>
+  </si>
+  <si>
+    <t>https://usastormroofing.com</t>
+  </si>
+  <si>
+    <t>USA Storm Roofing and Construction Group</t>
+  </si>
+  <si>
+    <t>Bob Bulgan</t>
+  </si>
+  <si>
+    <t>571-653-1241</t>
+  </si>
+  <si>
+    <t>info@usastormroofing.com</t>
+  </si>
+  <si>
+    <t>johnny@usastormroofing.com</t>
+  </si>
+  <si>
+    <t>https://coldemail-ruddy.vercel.app/coldemail/USAStormRoofingandConstructionGroup/index.html</t>
+  </si>
+  <si>
+    <t>Services: roof replacements, repairs, siding, gutters, windows, storm damage. Owner: Bob Bulgan. A+ BBB.</t>
   </si>
 </sst>
 </file>
@@ -723,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1324,6 +1357,59 @@
         <v>115</v>
       </c>
     </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>125</v>
+      </c>
+      <c r="N12" s="2">
+        <v>46259</v>
+      </c>
+      <c r="O12" t="s">
+        <v>84</v>
+      </c>
+      <c r="T12" t="s">
+        <v>35</v>
+      </c>
+      <c r="V12" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1118,9 +1118,77 @@
         <v>Online roofing materials retailer. Operating since 2011. Associated with MBM SW Ltd (Mammoth Roofing). Helen Jarvis is Director.</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Roofing</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Torquay, Devon</v>
+      </c>
+      <c r="C14" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D14" t="str">
+        <v>NA</v>
+      </c>
+      <c r="E14" t="str">
+        <v>NA</v>
+      </c>
+      <c r="F14" t="str">
+        <v>https://ukroofingandbuilding.co.uk</v>
+      </c>
+      <c r="G14" t="str">
+        <v>UK Roofing &amp; Building Limited</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Will Appleton</v>
+      </c>
+      <c r="I14" t="str">
+        <v>07441 945690</v>
+      </c>
+      <c r="J14" t="str">
+        <v>info@ukroofingandbuilding.co.uk</v>
+      </c>
+      <c r="K14" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L14" t="str">
+        <v>NA</v>
+      </c>
+      <c r="M14" t="str">
+        <v>https://coldemail-ruddy.vercel.app/coldemail/UKRoofingandBuildingLimited/index.html</v>
+      </c>
+      <c r="N14" t="str">
+        <v>2026-08-27</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Google Maps</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v>New</v>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
+      <c r="V14" t="str">
+        <v>Based in Torquay/Devon. Owner is Will Appleton. Serves multiple regions.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/leads.xlsx
+++ b/leads.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1186,9 +1186,77 @@
         <v>Based in Torquay/Devon. Owner is Will Appleton. Serves multiple regions.</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Roofing</v>
+      </c>
+      <c r="B15" t="str">
+        <v>London, England</v>
+      </c>
+      <c r="C15" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D15" t="str">
+        <v>NA</v>
+      </c>
+      <c r="E15" t="str">
+        <v>NA</v>
+      </c>
+      <c r="F15" t="str">
+        <v>https://ukroofsurveys.co.uk</v>
+      </c>
+      <c r="G15" t="str">
+        <v>UK Roof Surveys Ltd</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Ashley Stephen Dowsing</v>
+      </c>
+      <c r="I15" t="str">
+        <v>03300535095</v>
+      </c>
+      <c r="J15" t="str">
+        <v>info@ukrss.co.uk</v>
+      </c>
+      <c r="K15" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L15" t="str">
+        <v>NA</v>
+      </c>
+      <c r="M15" t="str">
+        <v>https://coldemail-ruddy.vercel.app/coldemail/UKRoofSurveysLtd/index.html</v>
+      </c>
+      <c r="N15" t="str">
+        <v>2026-08-27</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Google Maps</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v>New</v>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
+      <c r="V15" t="str">
+        <v>Independent roof surveying company. Does not undertake repairs. Owner is Ashley Stephen Dowsing. Nationwide service.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/leads.xlsx
+++ b/leads.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1254,9 +1254,77 @@
         <v>Independent roof surveying company. Does not undertake repairs. Owner is Ashley Stephen Dowsing. Nationwide service.</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Roofing</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Wolverhampton, West Midlands</v>
+      </c>
+      <c r="C16" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D16" t="str">
+        <v>NA</v>
+      </c>
+      <c r="E16" t="str">
+        <v>NA</v>
+      </c>
+      <c r="F16" t="str">
+        <v>https://ukrubberroofing.co.uk</v>
+      </c>
+      <c r="G16" t="str">
+        <v>UK Rubber Roofing Ltd</v>
+      </c>
+      <c r="H16" t="str">
+        <v>John Clifford Cooper</v>
+      </c>
+      <c r="I16" t="str">
+        <v>01902 602808</v>
+      </c>
+      <c r="J16" t="str">
+        <v>james@ukrubberroofing.co.uk</v>
+      </c>
+      <c r="K16" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L16" t="str">
+        <v>NA</v>
+      </c>
+      <c r="M16" t="str">
+        <v>https://coldemail-ruddy.vercel.app/coldemail/UKRubberRoofingLtd/index.html</v>
+      </c>
+      <c r="N16" t="str">
+        <v>2026-08-27</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Google Maps</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v>New</v>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
+      <c r="V16" t="str">
+        <v>Supplier and installer of rubber roofing products. Director is John Clifford Cooper.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V16"/>
   </ignoredErrors>
 </worksheet>
 </file>